--- a/data/bak.xlsx
+++ b/data/bak.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27980" windowHeight="11780"/>
+    <workbookView windowWidth="26860" windowHeight="11460"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2">
-        <v>998</v>
+        <v>-2</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3">
-        <v>999</v>
+        <v>-1</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>

--- a/data/bak.xlsx
+++ b/data/bak.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26860" windowHeight="11460"/>
+    <workbookView windowWidth="30240" windowHeight="12760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -53,6 +53,9 @@
     <t>create_time</t>
   </si>
   <si>
+    <t>investor_id</t>
+  </si>
+  <si>
     <t>data_type</t>
   </si>
   <si>
@@ -66,6 +69,9 @@
   </si>
   <si>
     <t>escort</t>
+  </si>
+  <si>
+    <t>car_type_limit</t>
   </si>
   <si>
     <t>交班点</t>
@@ -696,11 +702,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1228,111 +1237,123 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2"/>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:15">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2">
+    <row r="2" s="1" customFormat="1" spans="1:12">
+      <c r="A2" s="1">
         <v>-2</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2">
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1">
         <v>0</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>1.31497</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>103.765</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="1">
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1">
         <v>0</v>
       </c>
-      <c r="K2" s="1">
+      <c r="J2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2">
         <v>0.999305555555556</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
+    <row r="3" s="1" customFormat="1" spans="1:12">
+      <c r="A3" s="1">
         <v>-1</v>
       </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1">
         <v>0</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>1.31314</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>103.752</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="1">
+      <c r="K3" s="2">
         <v>0</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="2">
         <v>0.999305555555556</v>
       </c>
     </row>
